--- a/output/R8_部門別原価計算書_4-8月.xlsx
+++ b/output/R8_部門別原価計算書_4-8月.xlsx
@@ -43,7 +43,7 @@
       <rPr>
         <b val="true"/>
         <sz val="14"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="Meiryo UI"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">年度　部門別原価計算書　月次推移（並製）</t>
@@ -54,7 +54,7 @@
       <rPr>
         <sz val="9"/>
         <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="Meiryo UI"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">各月シートの「並製」列を参照。累計列は合計（人数・点数・部数・平均ロットは</t>
@@ -73,7 +73,7 @@
       <rPr>
         <sz val="9"/>
         <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="Meiryo UI"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">か月平均）。緑字＝各月シートへの参照式</t>
@@ -97,7 +97,7 @@
       <rPr>
         <b val="true"/>
         <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="Meiryo UI"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">月</t>
@@ -118,7 +118,7 @@
       <rPr>
         <b val="true"/>
         <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="Meiryo UI"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">月</t>
@@ -139,7 +139,7 @@
       <rPr>
         <b val="true"/>
         <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="Meiryo UI"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">月</t>
@@ -160,7 +160,7 @@
       <rPr>
         <b val="true"/>
         <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="Meiryo UI"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">月</t>
@@ -181,7 +181,7 @@
       <rPr>
         <b val="true"/>
         <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="Meiryo UI"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">月</t>
@@ -430,7 +430,7 @@
       <rPr>
         <b val="true"/>
         <sz val="14"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="Meiryo UI"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">年度　部門別原価計算書　月次推移（上製）</t>
@@ -441,7 +441,7 @@
       <rPr>
         <sz val="9"/>
         <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="Meiryo UI"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">各月シートの「上製」列を参照。累計列は合計（人数・点数・部数・平均ロットは</t>
@@ -460,7 +460,7 @@
       <rPr>
         <sz val="9"/>
         <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="Meiryo UI"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">か月平均）。緑字＝各月シートへの参照式</t>
@@ -481,7 +481,7 @@
       <rPr>
         <b val="true"/>
         <sz val="14"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="Meiryo UI"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">年度　部門別原価計算書　月次推移（合計）</t>
@@ -492,7 +492,7 @@
       <rPr>
         <sz val="9"/>
         <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="Meiryo UI"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">各月シートの「小計」列（上製＋並製）を参照。材料仕入高のみ原本「合計」列。累計列は合計（人数・点数・部数・平均ロットは</t>
@@ -511,7 +511,7 @@
       <rPr>
         <sz val="9"/>
         <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="Meiryo UI"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">か月平均）。緑字＝各月シートへの参照式</t>
@@ -535,7 +535,7 @@
       <rPr>
         <b val="true"/>
         <sz val="14"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="Meiryo UI"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">年度　部門別原価計算書　</t>
@@ -554,7 +554,7 @@
       <rPr>
         <b val="true"/>
         <sz val="14"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="Meiryo UI"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">月分</t>
@@ -565,7 +565,7 @@
       <rPr>
         <sz val="9"/>
         <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="Meiryo UI"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">出力日：</t>
@@ -584,7 +584,7 @@
       <rPr>
         <sz val="9"/>
         <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="Meiryo UI"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">　　☆ 変動費　△ 固定費　○ 入力　　※原本で</t>
@@ -603,7 +603,7 @@
       <rPr>
         <sz val="9"/>
         <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="Meiryo UI"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">除算エラー表示のセルは「－」で表示</t>
@@ -649,7 +649,7 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="Meiryo UI"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">売上高</t>
@@ -671,7 +671,7 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="Meiryo UI"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">人数</t>
@@ -693,7 +693,7 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="Meiryo UI"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">点数</t>
@@ -715,7 +715,7 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="Meiryo UI"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">部数</t>
@@ -761,7 +761,7 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="Meiryo UI"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">人あたり加工高</t>
@@ -780,7 +780,7 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="Meiryo UI"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">冊あたり平均単価（運送賃含む）</t>
@@ -799,7 +799,7 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="Meiryo UI"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">冊あたり平均単価（加工収入のみ</t>
@@ -827,7 +827,7 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="Meiryo UI"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">人あたり平均給与</t>
@@ -846,7 +846,7 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="Meiryo UI"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">人あたり人件費</t>
@@ -876,7 +876,7 @@
       <rPr>
         <sz val="9"/>
         <color rgb="FFE0007A"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="Meiryo UI"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">以上</t>
@@ -900,7 +900,7 @@
       <rPr>
         <sz val="9"/>
         <color rgb="FFE0007A"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="Meiryo UI"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">以下</t>
@@ -919,7 +919,7 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="Meiryo UI"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">人あたり加工高対給与比率</t>
@@ -930,7 +930,7 @@
       <rPr>
         <sz val="9"/>
         <color rgb="FFE0007A"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="Meiryo UI"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">給与の</t>
@@ -949,7 +949,7 @@
       <rPr>
         <sz val="9"/>
         <color rgb="FFE0007A"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="Meiryo UI"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">倍</t>
@@ -973,7 +973,7 @@
       <rPr>
         <sz val="9"/>
         <color rgb="FFE0007A"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="Meiryo UI"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">以下</t>
@@ -993,7 +993,7 @@
       <rPr>
         <sz val="9"/>
         <color rgb="FFE0007A"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="Meiryo UI"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">目標</t>
@@ -1012,7 +1012,7 @@
       <rPr>
         <sz val="9"/>
         <color rgb="FFE0007A"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="Meiryo UI"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">以上</t>
@@ -1033,7 +1033,7 @@
       <rPr>
         <b val="true"/>
         <sz val="14"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="Meiryo UI"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">年度　部門別原価計算書　</t>
@@ -1052,7 +1052,7 @@
       <rPr>
         <b val="true"/>
         <sz val="14"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="Meiryo UI"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">月分</t>
@@ -1073,7 +1073,7 @@
       <rPr>
         <b val="true"/>
         <sz val="14"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="Meiryo UI"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">年度　部門別原価計算書　</t>
@@ -1092,7 +1092,7 @@
       <rPr>
         <b val="true"/>
         <sz val="14"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="Meiryo UI"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">月分</t>
@@ -1113,7 +1113,7 @@
       <rPr>
         <b val="true"/>
         <sz val="14"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="Meiryo UI"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">年度　部門別原価計算書　</t>
@@ -1132,7 +1132,7 @@
       <rPr>
         <b val="true"/>
         <sz val="14"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="Meiryo UI"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">月分</t>
@@ -1153,7 +1153,7 @@
       <rPr>
         <b val="true"/>
         <sz val="14"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="Meiryo UI"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">年度　部門別原価計算書　</t>
@@ -1172,7 +1172,7 @@
       <rPr>
         <b val="true"/>
         <sz val="14"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="Meiryo UI"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">月分</t>
@@ -1195,23 +1195,23 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Meiryo UI"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="Meiryo UI"/>
       <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="Meiryo UI"/>
       <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="Meiryo UI"/>
       <family val="0"/>
     </font>
     <font>
@@ -1224,13 +1224,13 @@
     <font>
       <b val="true"/>
       <sz val="14"/>
-      <name val="WenQuanYi Zen Hei"/>
+      <name val="Meiryo UI"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF595959"/>
-      <name val="WenQuanYi Zen Hei"/>
+      <name val="Meiryo UI"/>
       <family val="2"/>
     </font>
     <font>
@@ -1250,7 +1250,7 @@
     <font>
       <b val="true"/>
       <sz val="10"/>
-      <name val="WenQuanYi Zen Hei"/>
+      <name val="Meiryo UI"/>
       <family val="2"/>
     </font>
     <font>
@@ -1261,7 +1261,7 @@
     </font>
     <font>
       <sz val="10"/>
-      <name val="WenQuanYi Zen Hei"/>
+      <name val="Meiryo UI"/>
       <family val="2"/>
     </font>
     <font>
@@ -1282,7 +1282,7 @@
     <font>
       <sz val="10"/>
       <color rgb="FF808080"/>
-      <name val="WenQuanYi Zen Hei"/>
+      <name val="Meiryo UI"/>
       <family val="2"/>
     </font>
     <font>
@@ -1310,7 +1310,7 @@
     <font>
       <sz val="9"/>
       <color rgb="FFE0007A"/>
-      <name val="WenQuanYi Zen Hei"/>
+      <name val="Meiryo UI"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -1659,13 +1659,13 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
-        <a:ea typeface=""/>
+        <a:latin typeface="Meiryo UI" pitchFamily="0" charset="1"/>
+        <a:ea typeface="Meiryo UI"/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
-        <a:ea typeface=""/>
+        <a:latin typeface="Meiryo UI" pitchFamily="0" charset="1"/>
+        <a:ea typeface="Meiryo UI"/>
         <a:cs typeface=""/>
       </a:minorFont>
     </a:fontScheme>
